--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_sticky_header.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_sticky_header.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="C2" t="n">
-        <v>64.5</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n">
-        <v>35.5</v>
+        <v>34.38</v>
       </c>
     </row>
   </sheetData>
